--- a/Thesis Forecasting/PAPER CONTEXT/tables/appendix_C_hyperparameters_configuration_all_models.xlsx
+++ b/Thesis Forecasting/PAPER CONTEXT/tables/appendix_C_hyperparameters_configuration_all_models.xlsx
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>158</v>
+        <v>203</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.15</v>
+        <v>0.75</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Yes (-0.005794 MW)</t>
+          <t>Yes (0.043468 MW)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>169</v>
+        <v>234</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.0005</v>
+        <v>0.0007</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Yes (0.002722 MW)</t>
+          <t>Yes (0.008800 MW)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>169</v>
+        <v>234</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Yes (0.001869 MW)</t>
+          <t>Yes (0.002246 MW)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>168</v>
+        <v>213</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.001</v>
+        <v>0.0003</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Yes (-0.013115 MW)</t>
+          <t>Yes (-0.020561 MW)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>171</v>
+        <v>276</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1.15</v>
+        <v>0.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Yes (-0.008944 MW)</t>
+          <t>Yes (-0.007211 MW)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>168</v>
+        <v>213</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.001</v>
+        <v>0.0003</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Yes (0.007462 MW)</t>
+          <t>Yes (0.007701 MW)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2764,7 +2764,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>158</v>
+        <v>203</v>
       </c>
       <c r="C2" t="n">
         <v>80</v>
@@ -2779,11 +2779,11 @@
         <v>32</v>
       </c>
       <c r="G2" t="n">
-        <v>1.15</v>
+        <v>0.75</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Yes (-0.005794 MW)</t>
+          <t>Yes (0.043468 MW)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -2809,13 +2809,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>169</v>
+        <v>234</v>
       </c>
       <c r="C3" t="n">
         <v>120</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0005</v>
+        <v>0.0007</v>
       </c>
       <c r="E3" t="n">
         <v>80</v>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Yes (0.002722 MW)</t>
+          <t>Yes (0.008800 MW)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>169</v>
+        <v>234</v>
       </c>
       <c r="C4" t="n">
         <v>180</v>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Yes (0.001869 MW)</t>
+          <t>Yes (0.002246 MW)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -2899,13 +2899,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>168</v>
+        <v>213</v>
       </c>
       <c r="C5" t="n">
         <v>180</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001</v>
+        <v>0.0003</v>
       </c>
       <c r="E5" t="n">
         <v>80</v>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Yes (-0.013115 MW)</t>
+          <t>Yes (-0.020561 MW)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2944,13 +2944,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>171</v>
+        <v>276</v>
       </c>
       <c r="C6" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0005</v>
+        <v>0.001</v>
       </c>
       <c r="E6" t="n">
         <v>80</v>
@@ -2959,11 +2959,11 @@
         <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>1.15</v>
+        <v>0.2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Yes (-0.008944 MW)</t>
+          <t>Yes (-0.007211 MW)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2989,13 +2989,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>168</v>
+        <v>213</v>
       </c>
       <c r="C7" t="n">
         <v>120</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001</v>
+        <v>0.0003</v>
       </c>
       <c r="E7" t="n">
         <v>80</v>
@@ -3004,11 +3004,11 @@
         <v>32</v>
       </c>
       <c r="G7" t="n">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Yes (0.007462 MW)</t>
+          <t>Yes (0.007701 MW)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
